--- a/backend/Combined_sheet_output_speed/GA/GA_2024_ABM.xlsx
+++ b/backend/Combined_sheet_output_speed/GA/GA_2024_ABM.xlsx
@@ -604,7 +604,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G6" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G7" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="8">
@@ -658,7 +658,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G8" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="9">
@@ -685,7 +685,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G9" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="10">
@@ -712,7 +712,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G10" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="11">
@@ -739,7 +739,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G11" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="12">
@@ -766,7 +766,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G12" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="13">
@@ -793,7 +793,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G13" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="14">
@@ -820,7 +820,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G14" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="15">
@@ -847,7 +847,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G15" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="16">
@@ -874,7 +874,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G16" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="17">
@@ -901,7 +901,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G17" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="18">
@@ -928,7 +928,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G18" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="19">
@@ -955,7 +955,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G19" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="20">
@@ -982,7 +982,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G20" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="21">
@@ -1009,7 +1009,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G21" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="22">
@@ -1036,7 +1036,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G22" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="23">
@@ -1063,7 +1063,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G23" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="24">
@@ -1090,7 +1090,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G24" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="25">
@@ -1117,7 +1117,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G25" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="26">
@@ -6421,16 +6421,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D26" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E26" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F26" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G26" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="27">
@@ -6448,16 +6448,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D27" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E27" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F27" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G27" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="28">
@@ -6475,16 +6475,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D28" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E28" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F28" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G28" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="29">
@@ -6502,16 +6502,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D29" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E29" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F29" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G29" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="30">
@@ -6529,16 +6529,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D30" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E30" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F30" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G30" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="31">
@@ -6556,16 +6556,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D31" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E31" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F31" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G31" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="32">
@@ -6583,16 +6583,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D32" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E32" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F32" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G32" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="33">
@@ -6610,16 +6610,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D33" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E33" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F33" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G33" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="34">
@@ -6637,16 +6637,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D34" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E34" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F34" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G34" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="35">
@@ -6664,16 +6664,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D35" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E35" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F35" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G35" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="36">
@@ -6691,16 +6691,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D36" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E36" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F36" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G36" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="37">
@@ -6718,16 +6718,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D37" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E37" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F37" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G37" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="38">
@@ -6745,16 +6745,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D38" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E38" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F38" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G38" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="39">
@@ -6772,16 +6772,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D39" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E39" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F39" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G39" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="40">
@@ -6799,16 +6799,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D40" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E40" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F40" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G40" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="41">
@@ -6826,16 +6826,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D41" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E41" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F41" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G41" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="42">
@@ -11059,16 +11059,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D2" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E2" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F2" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="3">
@@ -11086,16 +11086,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D3" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E3" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F3" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="4">
@@ -11113,16 +11113,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D4" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E4" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F4" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="5">
@@ -11140,16 +11140,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D5" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E5" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F5" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="6">
@@ -12139,16 +12139,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D42" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E42" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F42" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G42" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="43">
@@ -12166,16 +12166,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D43" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E43" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F43" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G43" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="44">
@@ -12193,16 +12193,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D44" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E44" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F44" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G44" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="45">
@@ -12220,16 +12220,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D45" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E45" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F45" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G45" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="46">
@@ -12247,16 +12247,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D46" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E46" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F46" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G46" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="47">
@@ -12274,16 +12274,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D47" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E47" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F47" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G47" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="48">
@@ -12301,16 +12301,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D48" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E48" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F48" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G48" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="49">
@@ -12328,16 +12328,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D49" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E49" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F49" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G49" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="50">
@@ -12355,16 +12355,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D50" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E50" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F50" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G50" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="51">
@@ -12382,16 +12382,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D51" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E51" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F51" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G51" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="52">
@@ -12409,16 +12409,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D52" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E52" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F52" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G52" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="53">
@@ -12436,16 +12436,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D53" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E53" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F53" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G53" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="54">
@@ -12463,16 +12463,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D54" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E54" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F54" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G54" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="55">
@@ -12490,16 +12490,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D55" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E55" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F55" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G55" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="56">
@@ -12517,16 +12517,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D56" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E56" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F56" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G56" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="57">
@@ -12544,16 +12544,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D57" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E57" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F57" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G57" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="58">
@@ -12571,16 +12571,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D58" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E58" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F58" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G58" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="59">
@@ -12598,16 +12598,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D59" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E59" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F59" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G59" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="60">
@@ -12625,16 +12625,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D60" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E60" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F60" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G60" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="61">
@@ -12652,16 +12652,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D61" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E61" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F61" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G61" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="62">
@@ -12679,16 +12679,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D62" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E62" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F62" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G62" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="63">
@@ -12706,16 +12706,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D63" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E63" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F63" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G63" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="64">
@@ -12733,16 +12733,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D64" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E64" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F64" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G64" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="65">
@@ -12760,16 +12760,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D65" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E65" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F65" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G65" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="66">
@@ -12787,16 +12787,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D66" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E66" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F66" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G66" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="67">
@@ -12814,16 +12814,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D67" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E67" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F67" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G67" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="68">
@@ -12841,16 +12841,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D68" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E68" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F68" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G68" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="69">
@@ -12868,16 +12868,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D69" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E69" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F69" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G69" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="70">
@@ -19636,10 +19636,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D26" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E26" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F26" t="n">
         <v>357.1591639871382</v>
@@ -19663,10 +19663,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D27" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E27" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F27" t="n">
         <v>357.1591639871382</v>
@@ -19690,10 +19690,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D28" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E28" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F28" t="n">
         <v>357.1591639871382</v>
@@ -19717,10 +19717,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D29" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E29" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F29" t="n">
         <v>357.1591639871382</v>
@@ -19744,10 +19744,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D30" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E30" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F30" t="n">
         <v>357.1591639871382</v>
@@ -19771,10 +19771,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D31" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E31" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F31" t="n">
         <v>357.1591639871382</v>
@@ -19798,10 +19798,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D32" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E32" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F32" t="n">
         <v>357.1591639871382</v>
@@ -19825,10 +19825,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D33" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E33" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F33" t="n">
         <v>357.1591639871382</v>
@@ -19852,10 +19852,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D34" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E34" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F34" t="n">
         <v>357.1591639871382</v>
@@ -19879,10 +19879,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D35" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E35" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F35" t="n">
         <v>357.1591639871382</v>
@@ -19906,10 +19906,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D36" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E36" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F36" t="n">
         <v>357.1591639871382</v>
@@ -19933,10 +19933,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D37" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E37" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F37" t="n">
         <v>357.1591639871382</v>
@@ -19960,10 +19960,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D38" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E38" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F38" t="n">
         <v>357.1591639871382</v>
@@ -19987,10 +19987,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D39" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E39" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F39" t="n">
         <v>357.1591639871382</v>
@@ -20014,10 +20014,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D40" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E40" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F40" t="n">
         <v>357.1591639871382</v>
@@ -20041,10 +20041,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D41" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E41" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F41" t="n">
         <v>357.1591639871382</v>
@@ -21148,10 +21148,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D82" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E82" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F82" t="n">
         <v>325.3271704180064</v>
@@ -21175,10 +21175,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D83" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E83" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F83" t="n">
         <v>325.3271704180064</v>
@@ -21202,10 +21202,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D84" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E84" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F84" t="n">
         <v>325.3271704180064</v>
@@ -21229,10 +21229,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D85" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E85" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F85" t="n">
         <v>325.3271704180064</v>
@@ -21256,10 +21256,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D86" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E86" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F86" t="n">
         <v>325.3271704180064</v>
@@ -21283,10 +21283,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D87" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E87" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F87" t="n">
         <v>325.3271704180064</v>
@@ -21310,10 +21310,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D88" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E88" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F88" t="n">
         <v>325.3271704180064</v>
@@ -21337,10 +21337,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D89" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E89" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F89" t="n">
         <v>325.3271704180064</v>
@@ -21364,10 +21364,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D90" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E90" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F90" t="n">
         <v>325.3271704180064</v>
@@ -21391,10 +21391,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D91" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E91" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F91" t="n">
         <v>325.3271704180064</v>
@@ -21418,10 +21418,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D92" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E92" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F92" t="n">
         <v>325.3271704180064</v>
@@ -21445,10 +21445,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D93" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E93" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F93" t="n">
         <v>325.3271704180064</v>
@@ -21472,10 +21472,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D94" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E94" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F94" t="n">
         <v>325.3271704180064</v>
@@ -21499,10 +21499,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D95" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E95" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F95" t="n">
         <v>325.3271704180064</v>
@@ -21526,10 +21526,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D96" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E96" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F96" t="n">
         <v>325.3271704180064</v>
@@ -21553,10 +21553,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D97" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E97" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F97" t="n">
         <v>325.3271704180064</v>
@@ -22276,7 +22276,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D26" t="n">
         <v>28.21085449100545</v>
@@ -22285,10 +22285,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F26" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G26" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="27">
@@ -22303,7 +22303,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D27" t="n">
         <v>28.21085449100545</v>
@@ -22312,10 +22312,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F27" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G27" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="28">
@@ -22330,7 +22330,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D28" t="n">
         <v>28.21085449100545</v>
@@ -22339,10 +22339,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F28" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G28" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="29">
@@ -22357,7 +22357,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D29" t="n">
         <v>28.21085449100545</v>
@@ -22366,10 +22366,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F29" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G29" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="30">
@@ -22384,7 +22384,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D30" t="n">
         <v>28.21085449100545</v>
@@ -22393,10 +22393,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F30" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G30" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="31">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D31" t="n">
         <v>28.21085449100545</v>
@@ -22420,10 +22420,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F31" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G31" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="32">
@@ -22438,7 +22438,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D32" t="n">
         <v>28.21085449100545</v>
@@ -22447,10 +22447,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F32" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G32" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="33">
@@ -22465,7 +22465,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D33" t="n">
         <v>28.21085449100545</v>
@@ -22474,10 +22474,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F33" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G33" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="34">
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D34" t="n">
         <v>28.21085449100545</v>
@@ -22501,10 +22501,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F34" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G34" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="35">
@@ -22519,7 +22519,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D35" t="n">
         <v>28.21085449100545</v>
@@ -22528,10 +22528,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F35" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G35" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="36">
@@ -22546,7 +22546,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D36" t="n">
         <v>28.21085449100545</v>
@@ -22555,10 +22555,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F36" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G36" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="37">
@@ -22573,7 +22573,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D37" t="n">
         <v>28.21085449100545</v>
@@ -22582,10 +22582,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F37" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G37" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="38">
@@ -22600,7 +22600,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D38" t="n">
         <v>28.21085449100545</v>
@@ -22609,10 +22609,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F38" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G38" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="39">
@@ -22627,7 +22627,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D39" t="n">
         <v>28.21085449100545</v>
@@ -22636,10 +22636,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F39" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G39" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="40">
@@ -22654,7 +22654,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D40" t="n">
         <v>28.21085449100545</v>
@@ -22663,10 +22663,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F40" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G40" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="41">
@@ -22681,7 +22681,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D41" t="n">
         <v>28.21085449100545</v>
@@ -22690,10 +22690,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F41" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G41" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="42">
@@ -23788,7 +23788,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D82" t="n">
         <v>28.74371242335771</v>
@@ -23797,10 +23797,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F82" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G82" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="83">
@@ -23815,7 +23815,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D83" t="n">
         <v>28.74371242335771</v>
@@ -23824,10 +23824,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F83" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G83" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="84">
@@ -23842,7 +23842,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D84" t="n">
         <v>28.74371242335771</v>
@@ -23851,10 +23851,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F84" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G84" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="85">
@@ -23869,7 +23869,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D85" t="n">
         <v>28.74371242335771</v>
@@ -23878,10 +23878,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F85" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G85" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="86">
@@ -23896,7 +23896,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D86" t="n">
         <v>28.74371242335771</v>
@@ -23905,10 +23905,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F86" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G86" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="87">
@@ -23923,7 +23923,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D87" t="n">
         <v>28.74371242335771</v>
@@ -23932,10 +23932,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F87" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G87" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="88">
@@ -23950,7 +23950,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D88" t="n">
         <v>28.74371242335771</v>
@@ -23959,10 +23959,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F88" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G88" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="89">
@@ -23977,7 +23977,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D89" t="n">
         <v>28.74371242335771</v>
@@ -23986,10 +23986,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F89" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G89" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="90">
@@ -24004,7 +24004,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D90" t="n">
         <v>28.74371242335771</v>
@@ -24013,10 +24013,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F90" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G90" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="91">
@@ -24031,7 +24031,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D91" t="n">
         <v>28.74371242335771</v>
@@ -24040,10 +24040,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F91" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G91" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="92">
@@ -24058,7 +24058,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D92" t="n">
         <v>28.74371242335771</v>
@@ -24067,10 +24067,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F92" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G92" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="93">
@@ -24085,7 +24085,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D93" t="n">
         <v>28.74371242335771</v>
@@ -24094,10 +24094,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F93" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G93" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="94">
@@ -24112,7 +24112,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D94" t="n">
         <v>28.74371242335771</v>
@@ -24121,10 +24121,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F94" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G94" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="95">
@@ -24139,7 +24139,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D95" t="n">
         <v>28.74371242335771</v>
@@ -24148,10 +24148,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F95" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G95" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="96">
@@ -24166,7 +24166,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D96" t="n">
         <v>28.74371242335771</v>
@@ -24175,10 +24175,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F96" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G96" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="97">
@@ -24193,7 +24193,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D97" t="n">
         <v>28.74371242335771</v>
@@ -24202,10 +24202,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F97" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G97" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
   </sheetData>
@@ -36682,16 +36682,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D70" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E70" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F70" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G70" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="71">
@@ -36709,16 +36709,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D71" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E71" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F71" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G71" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="72">
@@ -36736,16 +36736,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D72" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E72" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F72" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G72" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="73">
@@ -36763,16 +36763,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D73" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E73" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F73" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G73" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="74">
@@ -36790,16 +36790,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D74" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E74" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F74" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G74" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="75">
@@ -36817,16 +36817,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D75" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E75" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F75" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G75" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="76">
@@ -36844,16 +36844,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D76" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E76" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F76" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G76" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="77">
@@ -36871,16 +36871,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D77" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E77" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F77" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G77" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="78">
@@ -36898,16 +36898,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D78" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E78" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F78" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="79">
@@ -36925,16 +36925,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D79" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E79" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F79" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="80">
@@ -36952,16 +36952,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D80" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E80" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F80" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G80" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="81">
@@ -36979,16 +36979,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D81" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E81" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F81" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G81" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="82">
@@ -37006,10 +37006,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D82" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E82" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F82" t="n">
         <v>200.2713675213675</v>
@@ -37033,10 +37033,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D83" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E83" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F83" t="n">
         <v>200.2713675213675</v>
@@ -37060,10 +37060,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D84" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E84" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F84" t="n">
         <v>200.2713675213675</v>
@@ -37087,10 +37087,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D85" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E85" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F85" t="n">
         <v>200.2713675213675</v>
@@ -37114,10 +37114,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D86" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E86" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F86" t="n">
         <v>200.2713675213675</v>
@@ -37141,10 +37141,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D87" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E87" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F87" t="n">
         <v>200.2713675213675</v>
@@ -37168,10 +37168,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D88" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E88" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F88" t="n">
         <v>200.2713675213675</v>
@@ -37195,10 +37195,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D89" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E89" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F89" t="n">
         <v>200.2713675213675</v>
@@ -37222,10 +37222,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D90" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E90" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F90" t="n">
         <v>200.2713675213675</v>
@@ -37249,10 +37249,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D91" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E91" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F91" t="n">
         <v>200.2713675213675</v>
@@ -37276,10 +37276,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D92" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E92" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F92" t="n">
         <v>200.2713675213675</v>
@@ -37303,10 +37303,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D93" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E93" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F93" t="n">
         <v>200.2713675213675</v>
@@ -37330,10 +37330,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D94" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E94" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F94" t="n">
         <v>200.2713675213675</v>
@@ -37357,10 +37357,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D95" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E95" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F95" t="n">
         <v>200.2713675213675</v>
@@ -37384,10 +37384,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D96" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E96" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F96" t="n">
         <v>200.2713675213675</v>
@@ -37411,10 +37411,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D97" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E97" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F97" t="n">
         <v>200.2713675213675</v>
@@ -37498,7 +37498,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="3">
@@ -37525,7 +37525,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G3" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="4">
@@ -37552,7 +37552,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G4" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="5">
@@ -37579,7 +37579,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="6">
@@ -38578,7 +38578,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G42" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="43">
@@ -38605,7 +38605,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G43" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="44">
@@ -38632,7 +38632,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G44" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="45">
@@ -38659,7 +38659,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G45" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="46">
@@ -38686,7 +38686,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G46" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="47">
@@ -38713,7 +38713,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G47" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="48">
@@ -38740,7 +38740,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G48" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="49">
@@ -38767,7 +38767,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G49" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="50">
@@ -38794,7 +38794,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G50" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="51">
@@ -38821,7 +38821,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G51" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="52">
@@ -38848,7 +38848,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G52" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="53">
@@ -38875,7 +38875,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G53" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="54">
@@ -38902,7 +38902,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G54" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="55">
@@ -38929,7 +38929,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G55" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="56">
@@ -38956,7 +38956,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G56" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="57">
@@ -38983,7 +38983,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G57" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="58">
@@ -39010,7 +39010,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G58" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="59">
@@ -39037,7 +39037,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G59" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="60">
@@ -39064,7 +39064,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G60" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="61">
@@ -39091,7 +39091,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G61" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="62">
@@ -39118,7 +39118,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G62" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="63">
@@ -39145,7 +39145,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G63" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="64">
@@ -39172,7 +39172,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G64" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="65">
@@ -39199,7 +39199,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G65" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="66">
@@ -39226,7 +39226,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G66" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="67">
@@ -39253,7 +39253,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G67" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="68">
@@ -39280,7 +39280,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G68" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="69">
@@ -39307,7 +39307,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G69" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="70">
@@ -39649,10 +39649,10 @@
         <v>209.725</v>
       </c>
       <c r="D82" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E82" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F82" t="n">
         <v>209.725</v>
@@ -39676,10 +39676,10 @@
         <v>209.725</v>
       </c>
       <c r="D83" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E83" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F83" t="n">
         <v>209.725</v>
@@ -39703,10 +39703,10 @@
         <v>209.725</v>
       </c>
       <c r="D84" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E84" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F84" t="n">
         <v>209.725</v>
@@ -39730,10 +39730,10 @@
         <v>209.725</v>
       </c>
       <c r="D85" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E85" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F85" t="n">
         <v>209.725</v>
@@ -39757,10 +39757,10 @@
         <v>209.725</v>
       </c>
       <c r="D86" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E86" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F86" t="n">
         <v>209.725</v>
@@ -39784,10 +39784,10 @@
         <v>209.725</v>
       </c>
       <c r="D87" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E87" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F87" t="n">
         <v>209.725</v>
@@ -39811,10 +39811,10 @@
         <v>209.725</v>
       </c>
       <c r="D88" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E88" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F88" t="n">
         <v>209.725</v>
@@ -39838,10 +39838,10 @@
         <v>209.725</v>
       </c>
       <c r="D89" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E89" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F89" t="n">
         <v>209.725</v>
@@ -39865,10 +39865,10 @@
         <v>209.725</v>
       </c>
       <c r="D90" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E90" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F90" t="n">
         <v>209.725</v>
@@ -39892,10 +39892,10 @@
         <v>209.725</v>
       </c>
       <c r="D91" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E91" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F91" t="n">
         <v>209.725</v>
@@ -39919,10 +39919,10 @@
         <v>209.725</v>
       </c>
       <c r="D92" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E92" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F92" t="n">
         <v>209.725</v>
@@ -39946,10 +39946,10 @@
         <v>209.725</v>
       </c>
       <c r="D93" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E93" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F93" t="n">
         <v>209.725</v>
@@ -39973,10 +39973,10 @@
         <v>209.725</v>
       </c>
       <c r="D94" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E94" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F94" t="n">
         <v>209.725</v>
@@ -40000,10 +40000,10 @@
         <v>209.725</v>
       </c>
       <c r="D95" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E95" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F95" t="n">
         <v>209.725</v>
@@ -40027,10 +40027,10 @@
         <v>209.725</v>
       </c>
       <c r="D96" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E96" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F96" t="n">
         <v>209.725</v>
@@ -40054,10 +40054,10 @@
         <v>209.725</v>
       </c>
       <c r="D97" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E97" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F97" t="n">
         <v>209.725</v>
@@ -42775,10 +42775,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D2" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E2" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F2" t="n">
         <v>107.2952044025157</v>
@@ -42802,10 +42802,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D3" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E3" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F3" t="n">
         <v>107.2952044025157</v>
@@ -42829,10 +42829,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D4" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E4" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F4" t="n">
         <v>107.2952044025157</v>
@@ -42856,10 +42856,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D5" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E5" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F5" t="n">
         <v>107.2952044025157</v>
@@ -43423,10 +43423,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D26" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E26" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F26" t="n">
         <v>356.122248427673</v>
@@ -43450,10 +43450,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D27" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E27" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F27" t="n">
         <v>356.122248427673</v>
@@ -43477,10 +43477,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D28" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E28" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F28" t="n">
         <v>356.122248427673</v>
@@ -43504,10 +43504,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D29" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E29" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F29" t="n">
         <v>356.122248427673</v>
@@ -43531,10 +43531,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D30" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E30" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F30" t="n">
         <v>356.122248427673</v>
@@ -43558,10 +43558,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D31" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E31" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F31" t="n">
         <v>356.122248427673</v>
@@ -43585,10 +43585,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D32" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E32" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F32" t="n">
         <v>356.122248427673</v>
@@ -43612,10 +43612,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D33" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E33" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F33" t="n">
         <v>356.122248427673</v>
@@ -43639,10 +43639,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D34" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E34" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F34" t="n">
         <v>356.122248427673</v>
@@ -43666,10 +43666,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D35" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E35" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F35" t="n">
         <v>356.122248427673</v>
@@ -43693,10 +43693,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D36" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E36" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F36" t="n">
         <v>356.122248427673</v>
@@ -43720,10 +43720,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D37" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E37" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F37" t="n">
         <v>356.122248427673</v>
@@ -43747,10 +43747,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D38" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E38" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F38" t="n">
         <v>356.122248427673</v>
@@ -43774,10 +43774,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D39" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E39" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F39" t="n">
         <v>356.122248427673</v>
@@ -43801,10 +43801,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D40" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E40" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F40" t="n">
         <v>356.122248427673</v>
@@ -43828,10 +43828,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D41" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E41" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F41" t="n">
         <v>356.122248427673</v>
@@ -43855,10 +43855,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D42" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E42" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F42" t="n">
         <v>107.2952044025157</v>
@@ -43882,10 +43882,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D43" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E43" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F43" t="n">
         <v>107.2952044025157</v>
@@ -43909,10 +43909,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D44" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E44" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F44" t="n">
         <v>107.2952044025157</v>
@@ -43936,10 +43936,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D45" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E45" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F45" t="n">
         <v>107.2952044025157</v>
@@ -43963,10 +43963,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D46" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E46" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F46" t="n">
         <v>107.2952044025157</v>
@@ -43990,10 +43990,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D47" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E47" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F47" t="n">
         <v>107.2952044025157</v>
@@ -44017,10 +44017,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D48" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E48" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F48" t="n">
         <v>107.2952044025157</v>
@@ -44044,10 +44044,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D49" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E49" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F49" t="n">
         <v>107.2952044025157</v>
@@ -44071,10 +44071,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D50" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E50" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F50" t="n">
         <v>107.2952044025157</v>
@@ -44098,10 +44098,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D51" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E51" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F51" t="n">
         <v>107.2952044025157</v>
@@ -44125,10 +44125,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D52" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E52" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F52" t="n">
         <v>107.2952044025157</v>
@@ -44152,10 +44152,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D53" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E53" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F53" t="n">
         <v>107.2952044025157</v>
@@ -44179,10 +44179,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D54" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E54" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F54" t="n">
         <v>107.2952044025157</v>
@@ -44206,10 +44206,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D55" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E55" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F55" t="n">
         <v>107.2952044025157</v>
@@ -44233,10 +44233,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D56" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E56" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F56" t="n">
         <v>107.2952044025157</v>
@@ -44260,10 +44260,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D57" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E57" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F57" t="n">
         <v>107.2952044025157</v>
@@ -44287,10 +44287,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D58" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E58" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F58" t="n">
         <v>107.2952044025157</v>
@@ -44314,10 +44314,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D59" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E59" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F59" t="n">
         <v>107.2952044025157</v>
@@ -44341,10 +44341,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D60" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E60" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F60" t="n">
         <v>107.2952044025157</v>
@@ -44368,10 +44368,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D61" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E61" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F61" t="n">
         <v>107.2952044025157</v>
@@ -44395,10 +44395,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D62" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E62" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F62" t="n">
         <v>107.2952044025157</v>
@@ -44422,10 +44422,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D63" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E63" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F63" t="n">
         <v>107.2952044025157</v>
@@ -44449,10 +44449,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D64" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E64" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F64" t="n">
         <v>107.2952044025157</v>
@@ -44476,10 +44476,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D65" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E65" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F65" t="n">
         <v>107.2952044025157</v>
@@ -44503,10 +44503,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D66" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E66" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F66" t="n">
         <v>107.2952044025157</v>
@@ -44530,10 +44530,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D67" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E67" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F67" t="n">
         <v>107.2952044025157</v>
@@ -44557,10 +44557,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D68" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E68" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F68" t="n">
         <v>107.2952044025157</v>
@@ -44584,10 +44584,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D69" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E69" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F69" t="n">
         <v>107.2952044025157</v>
@@ -45427,7 +45427,7 @@
         <v>36.05625</v>
       </c>
       <c r="G2" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="3">
@@ -45454,7 +45454,7 @@
         <v>36.05625</v>
       </c>
       <c r="G3" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="4">
@@ -45481,7 +45481,7 @@
         <v>36.05625</v>
       </c>
       <c r="G4" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="5">
@@ -45508,7 +45508,7 @@
         <v>36.05625</v>
       </c>
       <c r="G5" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="6">
@@ -45535,7 +45535,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G6" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="7">
@@ -45562,7 +45562,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G7" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="8">
@@ -45589,7 +45589,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G8" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="9">
@@ -45616,7 +45616,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G9" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="10">
@@ -45643,7 +45643,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G10" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="11">
@@ -45670,7 +45670,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G11" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="12">
@@ -45697,7 +45697,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G12" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="13">
@@ -45724,7 +45724,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G13" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="14">
@@ -45751,7 +45751,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G14" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="15">
@@ -45778,7 +45778,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G15" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="16">
@@ -45805,7 +45805,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G16" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="17">
@@ -45832,7 +45832,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G17" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="18">
@@ -45859,7 +45859,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G18" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="19">
@@ -45886,7 +45886,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G19" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="20">
@@ -45913,7 +45913,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G20" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="21">
@@ -45940,7 +45940,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G21" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="22">
@@ -45967,7 +45967,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G22" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="23">
@@ -45994,7 +45994,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G23" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="24">
@@ -46021,7 +46021,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G24" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="25">
@@ -46048,7 +46048,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G25" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="26">
@@ -46507,7 +46507,7 @@
         <v>36.05625</v>
       </c>
       <c r="G42" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="43">
@@ -46534,7 +46534,7 @@
         <v>36.05625</v>
       </c>
       <c r="G43" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="44">
@@ -46561,7 +46561,7 @@
         <v>36.05625</v>
       </c>
       <c r="G44" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="45">
@@ -46588,7 +46588,7 @@
         <v>36.05625</v>
       </c>
       <c r="G45" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="46">
@@ -46615,7 +46615,7 @@
         <v>36.05625</v>
       </c>
       <c r="G46" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="47">
@@ -46642,7 +46642,7 @@
         <v>36.05625</v>
       </c>
       <c r="G47" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="48">
@@ -46669,7 +46669,7 @@
         <v>36.05625</v>
       </c>
       <c r="G48" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="49">
@@ -46696,7 +46696,7 @@
         <v>36.05625</v>
       </c>
       <c r="G49" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="50">
@@ -46723,7 +46723,7 @@
         <v>36.05625</v>
       </c>
       <c r="G50" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="51">
@@ -46750,7 +46750,7 @@
         <v>36.05625</v>
       </c>
       <c r="G51" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="52">
@@ -46777,7 +46777,7 @@
         <v>36.05625</v>
       </c>
       <c r="G52" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="53">
@@ -46804,7 +46804,7 @@
         <v>36.05625</v>
       </c>
       <c r="G53" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="54">
@@ -46831,7 +46831,7 @@
         <v>36.05625</v>
       </c>
       <c r="G54" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="55">
@@ -46858,7 +46858,7 @@
         <v>36.05625</v>
       </c>
       <c r="G55" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="56">
@@ -46885,7 +46885,7 @@
         <v>36.05625</v>
       </c>
       <c r="G56" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="57">
@@ -46912,7 +46912,7 @@
         <v>36.05625</v>
       </c>
       <c r="G57" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="58">
@@ -46939,7 +46939,7 @@
         <v>36.05625</v>
       </c>
       <c r="G58" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="59">
@@ -46966,7 +46966,7 @@
         <v>36.05625</v>
       </c>
       <c r="G59" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="60">
@@ -46993,7 +46993,7 @@
         <v>36.05625</v>
       </c>
       <c r="G60" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="61">
@@ -47020,7 +47020,7 @@
         <v>36.05625</v>
       </c>
       <c r="G61" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="62">
@@ -47047,7 +47047,7 @@
         <v>36.05625</v>
       </c>
       <c r="G62" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="63">
@@ -47074,7 +47074,7 @@
         <v>36.05625</v>
       </c>
       <c r="G63" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="64">
@@ -47101,7 +47101,7 @@
         <v>36.05625</v>
       </c>
       <c r="G64" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="65">
@@ -47128,7 +47128,7 @@
         <v>36.05625</v>
       </c>
       <c r="G65" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="66">
@@ -47155,7 +47155,7 @@
         <v>36.05625</v>
       </c>
       <c r="G66" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="67">
@@ -47182,7 +47182,7 @@
         <v>36.05625</v>
       </c>
       <c r="G67" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="68">
@@ -47209,7 +47209,7 @@
         <v>36.05625</v>
       </c>
       <c r="G68" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="69">
@@ -47236,7 +47236,7 @@
         <v>36.05625</v>
       </c>
       <c r="G69" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="70">
@@ -50704,16 +50704,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D2" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E2" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F2" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G2" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="3">
@@ -50731,16 +50731,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D3" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E3" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F3" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G3" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="4">
@@ -50758,16 +50758,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D4" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E4" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F4" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G4" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="5">
@@ -50785,16 +50785,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D5" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E5" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F5" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G5" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="6">
@@ -50812,16 +50812,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D6" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E6" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F6" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G6" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="7">
@@ -50839,16 +50839,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D7" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E7" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F7" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G7" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="8">
@@ -50866,16 +50866,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D8" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E8" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F8" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G8" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="9">
@@ -50893,16 +50893,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D9" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E9" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F9" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G9" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="10">
@@ -50920,16 +50920,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D10" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E10" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F10" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G10" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="11">
@@ -50947,16 +50947,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D11" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E11" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F11" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G11" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="12">
@@ -50974,16 +50974,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D12" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E12" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F12" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G12" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="13">
@@ -51001,16 +51001,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D13" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E13" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F13" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G13" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="14">
@@ -51028,16 +51028,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D14" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E14" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F14" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G14" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="15">
@@ -51055,16 +51055,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D15" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E15" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F15" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G15" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="16">
@@ -51082,16 +51082,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D16" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E16" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F16" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G16" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="17">
@@ -51109,16 +51109,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D17" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E17" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F17" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G17" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="18">
@@ -51136,16 +51136,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D18" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E18" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F18" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G18" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="19">
@@ -51163,16 +51163,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D19" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E19" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F19" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G19" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="20">
@@ -51190,16 +51190,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D20" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E20" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F20" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G20" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="21">
@@ -51217,16 +51217,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D21" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E21" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F21" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G21" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="22">
@@ -51244,16 +51244,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D22" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E22" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F22" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G22" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="23">
@@ -51271,16 +51271,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D23" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E23" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F23" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G23" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="24">
@@ -51298,16 +51298,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D24" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E24" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F24" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G24" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="25">
@@ -51325,16 +51325,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D25" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E25" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F25" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G25" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="26">
@@ -51784,16 +51784,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D42" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E42" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F42" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G42" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="43">
@@ -51811,16 +51811,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D43" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E43" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F43" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G43" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="44">
@@ -51838,16 +51838,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D44" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E44" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F44" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G44" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="45">
@@ -51865,16 +51865,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D45" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E45" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F45" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G45" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="46">
@@ -51892,16 +51892,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D46" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E46" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F46" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G46" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="47">
@@ -51919,16 +51919,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D47" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E47" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F47" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G47" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="48">
@@ -51946,16 +51946,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D48" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E48" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F48" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G48" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="49">
@@ -51973,16 +51973,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D49" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E49" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F49" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G49" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="50">
@@ -52000,16 +52000,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D50" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E50" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F50" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G50" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="51">
@@ -52027,16 +52027,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D51" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E51" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F51" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G51" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="52">
@@ -52054,16 +52054,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D52" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E52" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F52" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G52" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="53">
@@ -52081,16 +52081,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D53" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E53" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F53" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G53" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="54">
@@ -52108,16 +52108,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D54" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E54" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F54" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G54" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="55">
@@ -52135,16 +52135,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D55" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E55" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F55" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G55" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="56">
@@ -52162,16 +52162,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D56" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E56" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F56" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G56" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="57">
@@ -52189,16 +52189,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D57" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E57" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F57" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G57" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="58">
@@ -52216,16 +52216,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D58" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E58" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F58" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G58" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="59">
@@ -52243,16 +52243,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D59" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E59" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F59" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G59" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="60">
@@ -52270,16 +52270,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D60" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E60" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F60" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G60" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="61">
@@ -52297,16 +52297,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D61" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E61" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F61" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G61" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="62">
@@ -52324,16 +52324,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D62" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E62" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F62" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G62" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="63">
@@ -52351,16 +52351,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D63" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E63" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F63" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G63" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="64">
@@ -52378,16 +52378,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D64" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E64" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F64" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G64" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="65">
@@ -52405,16 +52405,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D65" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E65" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F65" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G65" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="66">
@@ -52432,16 +52432,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D66" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E66" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F66" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G66" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="67">
@@ -52459,16 +52459,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D67" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E67" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F67" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G67" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="68">
@@ -52486,16 +52486,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D68" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E68" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F68" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G68" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="69">
@@ -52513,16 +52513,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D69" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E69" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F69" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G69" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="70">

--- a/backend/Combined_sheet_output_speed/GA/GA_2024_ABM.xlsx
+++ b/backend/Combined_sheet_output_speed/GA/GA_2024_ABM.xlsx
@@ -1,32 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="tract=13121001001" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="tract=13121001002" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="tract=13121001201" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="tract=13121001202" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="tract=13121001800" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="tract=13121001900" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="tract=13121002100" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="tract=13121002600" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="tract=13121002800" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="tract=13121003500" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="tract=13121003600" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="tract=13121003800" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="tract=13121004300" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="tract=13121004400" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="tract=13121004800" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="tract=13121004900" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="tract=13121005800" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="tract=13121011800" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="tract=13121011900" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="tract=13121012000" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121001001" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121001002" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121001201" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121001202" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121001800" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121001900" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121002100" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121002600" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121002800" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121003500" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121003600" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121003800" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121004300" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121004400" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121004800" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121004900" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121005800" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121011800" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121011900" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tract=13121012000" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -604,7 +604,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G6" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G7" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="8">
@@ -658,7 +658,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G8" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="9">
@@ -685,7 +685,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G9" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="10">
@@ -712,7 +712,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G10" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="11">
@@ -739,7 +739,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G11" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="12">
@@ -766,7 +766,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G12" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="13">
@@ -793,7 +793,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G13" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="14">
@@ -820,7 +820,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G14" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="15">
@@ -847,7 +847,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G15" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="16">
@@ -874,7 +874,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G16" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="17">
@@ -901,7 +901,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G17" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="18">
@@ -928,7 +928,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G18" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="19">
@@ -955,7 +955,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G19" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="20">
@@ -982,7 +982,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G20" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="21">
@@ -1009,7 +1009,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G21" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="22">
@@ -1036,7 +1036,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G22" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="23">
@@ -1063,7 +1063,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G23" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="24">
@@ -1090,7 +1090,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G24" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="25">
@@ -1117,7 +1117,7 @@
         <v>553.8222222222222</v>
       </c>
       <c r="G25" t="n">
-        <v>18.40076689247406</v>
+        <v>18.40076689247405</v>
       </c>
     </row>
     <row r="26">
@@ -6421,16 +6421,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D26" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E26" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F26" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G26" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="27">
@@ -6448,16 +6448,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D27" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E27" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F27" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G27" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="28">
@@ -6475,16 +6475,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D28" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E28" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F28" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G28" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="29">
@@ -6502,16 +6502,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D29" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E29" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F29" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G29" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="30">
@@ -6529,16 +6529,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D30" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E30" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F30" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G30" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="31">
@@ -6556,16 +6556,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D31" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E31" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F31" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G31" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="32">
@@ -6583,16 +6583,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D32" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E32" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F32" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G32" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="33">
@@ -6610,16 +6610,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D33" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E33" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F33" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G33" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="34">
@@ -6637,16 +6637,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D34" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E34" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F34" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G34" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="35">
@@ -6664,16 +6664,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D35" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E35" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F35" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G35" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="36">
@@ -6691,16 +6691,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D36" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E36" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F36" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G36" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="37">
@@ -6718,16 +6718,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D37" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E37" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F37" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G37" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="38">
@@ -6745,16 +6745,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D38" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E38" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F38" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G38" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="39">
@@ -6772,16 +6772,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D39" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E39" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F39" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G39" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="40">
@@ -6799,16 +6799,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D40" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E40" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F40" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G40" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="41">
@@ -6826,16 +6826,16 @@
         <v>142.2835365853659</v>
       </c>
       <c r="D41" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="E41" t="n">
-        <v>19.18779709264663</v>
+        <v>19.18779709264664</v>
       </c>
       <c r="F41" t="n">
         <v>142.2835365853659</v>
       </c>
       <c r="G41" t="n">
-        <v>7.415313800659971</v>
+        <v>7.41531380065997</v>
       </c>
     </row>
     <row r="42">
@@ -11059,16 +11059,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D2" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E2" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F2" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="3">
@@ -11086,16 +11086,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D3" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E3" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F3" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="4">
@@ -11113,16 +11113,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D4" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E4" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F4" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="5">
@@ -11140,16 +11140,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D5" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E5" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F5" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="6">
@@ -12139,16 +12139,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D42" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E42" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F42" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G42" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="43">
@@ -12166,16 +12166,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D43" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E43" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F43" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G43" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="44">
@@ -12193,16 +12193,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D44" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E44" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F44" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G44" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="45">
@@ -12220,16 +12220,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D45" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E45" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F45" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G45" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="46">
@@ -12247,16 +12247,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D46" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E46" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F46" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G46" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="47">
@@ -12274,16 +12274,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D47" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E47" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F47" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G47" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="48">
@@ -12301,16 +12301,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D48" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E48" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F48" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G48" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="49">
@@ -12328,16 +12328,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D49" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E49" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F49" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G49" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="50">
@@ -12355,16 +12355,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D50" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E50" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F50" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G50" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="51">
@@ -12382,16 +12382,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D51" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E51" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F51" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G51" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="52">
@@ -12409,16 +12409,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D52" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E52" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F52" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G52" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="53">
@@ -12436,16 +12436,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D53" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E53" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F53" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G53" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="54">
@@ -12463,16 +12463,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D54" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E54" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F54" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G54" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="55">
@@ -12490,16 +12490,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D55" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E55" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F55" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G55" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="56">
@@ -12517,16 +12517,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D56" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E56" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F56" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G56" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="57">
@@ -12544,16 +12544,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D57" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E57" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F57" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G57" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="58">
@@ -12571,16 +12571,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D58" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E58" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F58" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G58" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="59">
@@ -12598,16 +12598,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D59" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E59" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F59" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G59" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="60">
@@ -12625,16 +12625,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D60" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E60" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F60" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G60" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="61">
@@ -12652,16 +12652,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D61" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E61" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F61" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G61" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="62">
@@ -12679,16 +12679,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D62" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E62" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F62" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G62" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="63">
@@ -12706,16 +12706,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D63" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E63" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F63" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G63" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="64">
@@ -12733,16 +12733,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D64" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E64" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F64" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G64" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="65">
@@ -12760,16 +12760,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D65" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E65" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F65" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G65" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="66">
@@ -12787,16 +12787,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D66" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E66" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F66" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G66" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="67">
@@ -12814,16 +12814,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D67" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E67" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F67" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G67" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="68">
@@ -12841,16 +12841,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D68" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E68" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F68" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G68" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="69">
@@ -12868,16 +12868,16 @@
         <v>17.7541095890411</v>
       </c>
       <c r="D69" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="E69" t="n">
-        <v>23.43647246260002</v>
+        <v>23.43647246260001</v>
       </c>
       <c r="F69" t="n">
         <v>17.7541095890411</v>
       </c>
       <c r="G69" t="n">
-        <v>0.7575418876442754</v>
+        <v>0.7575418876442755</v>
       </c>
     </row>
     <row r="70">
@@ -19636,10 +19636,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D26" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E26" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F26" t="n">
         <v>357.1591639871382</v>
@@ -19663,10 +19663,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D27" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E27" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F27" t="n">
         <v>357.1591639871382</v>
@@ -19690,10 +19690,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D28" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E28" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F28" t="n">
         <v>357.1591639871382</v>
@@ -19717,10 +19717,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D29" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E29" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F29" t="n">
         <v>357.1591639871382</v>
@@ -19744,10 +19744,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D30" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E30" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F30" t="n">
         <v>357.1591639871382</v>
@@ -19771,10 +19771,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D31" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E31" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F31" t="n">
         <v>357.1591639871382</v>
@@ -19798,10 +19798,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D32" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E32" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F32" t="n">
         <v>357.1591639871382</v>
@@ -19825,10 +19825,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D33" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E33" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F33" t="n">
         <v>357.1591639871382</v>
@@ -19852,10 +19852,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D34" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E34" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F34" t="n">
         <v>357.1591639871382</v>
@@ -19879,10 +19879,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D35" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E35" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F35" t="n">
         <v>357.1591639871382</v>
@@ -19906,10 +19906,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D36" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E36" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F36" t="n">
         <v>357.1591639871382</v>
@@ -19933,10 +19933,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D37" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E37" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F37" t="n">
         <v>357.1591639871382</v>
@@ -19960,10 +19960,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D38" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E38" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F38" t="n">
         <v>357.1591639871382</v>
@@ -19987,10 +19987,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D39" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E39" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F39" t="n">
         <v>357.1591639871382</v>
@@ -20014,10 +20014,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D40" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E40" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F40" t="n">
         <v>357.1591639871382</v>
@@ -20041,10 +20041,10 @@
         <v>357.1591639871382</v>
       </c>
       <c r="D41" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="E41" t="n">
-        <v>24.47244341499522</v>
+        <v>24.47244341499521</v>
       </c>
       <c r="F41" t="n">
         <v>357.1591639871382</v>
@@ -21148,10 +21148,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D82" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E82" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F82" t="n">
         <v>325.3271704180064</v>
@@ -21175,10 +21175,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D83" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E83" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F83" t="n">
         <v>325.3271704180064</v>
@@ -21202,10 +21202,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D84" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E84" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F84" t="n">
         <v>325.3271704180064</v>
@@ -21229,10 +21229,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D85" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E85" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F85" t="n">
         <v>325.3271704180064</v>
@@ -21256,10 +21256,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D86" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E86" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F86" t="n">
         <v>325.3271704180064</v>
@@ -21283,10 +21283,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D87" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E87" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F87" t="n">
         <v>325.3271704180064</v>
@@ -21310,10 +21310,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D88" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E88" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F88" t="n">
         <v>325.3271704180064</v>
@@ -21337,10 +21337,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D89" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E89" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F89" t="n">
         <v>325.3271704180064</v>
@@ -21364,10 +21364,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D90" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E90" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F90" t="n">
         <v>325.3271704180064</v>
@@ -21391,10 +21391,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D91" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E91" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F91" t="n">
         <v>325.3271704180064</v>
@@ -21418,10 +21418,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D92" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E92" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F92" t="n">
         <v>325.3271704180064</v>
@@ -21445,10 +21445,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D93" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E93" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F93" t="n">
         <v>325.3271704180064</v>
@@ -21472,10 +21472,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D94" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E94" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F94" t="n">
         <v>325.3271704180064</v>
@@ -21499,10 +21499,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D95" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E95" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F95" t="n">
         <v>325.3271704180064</v>
@@ -21526,10 +21526,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D96" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E96" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F96" t="n">
         <v>325.3271704180064</v>
@@ -21553,10 +21553,10 @@
         <v>325.3271704180064</v>
       </c>
       <c r="D97" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="E97" t="n">
-        <v>24.74917575580023</v>
+        <v>24.74917575580024</v>
       </c>
       <c r="F97" t="n">
         <v>325.3271704180064</v>
@@ -22276,7 +22276,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D26" t="n">
         <v>28.21085449100545</v>
@@ -22285,10 +22285,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F26" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G26" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="27">
@@ -22303,7 +22303,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D27" t="n">
         <v>28.21085449100545</v>
@@ -22312,10 +22312,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F27" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G27" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="28">
@@ -22330,7 +22330,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D28" t="n">
         <v>28.21085449100545</v>
@@ -22339,10 +22339,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F28" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G28" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="29">
@@ -22357,7 +22357,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D29" t="n">
         <v>28.21085449100545</v>
@@ -22366,10 +22366,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F29" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G29" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="30">
@@ -22384,7 +22384,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D30" t="n">
         <v>28.21085449100545</v>
@@ -22393,10 +22393,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F30" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G30" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="31">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D31" t="n">
         <v>28.21085449100545</v>
@@ -22420,10 +22420,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F31" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G31" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="32">
@@ -22438,7 +22438,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D32" t="n">
         <v>28.21085449100545</v>
@@ -22447,10 +22447,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F32" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G32" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="33">
@@ -22465,7 +22465,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D33" t="n">
         <v>28.21085449100545</v>
@@ -22474,10 +22474,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F33" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G33" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="34">
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D34" t="n">
         <v>28.21085449100545</v>
@@ -22501,10 +22501,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F34" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G34" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="35">
@@ -22519,7 +22519,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D35" t="n">
         <v>28.21085449100545</v>
@@ -22528,10 +22528,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F35" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G35" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="36">
@@ -22546,7 +22546,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D36" t="n">
         <v>28.21085449100545</v>
@@ -22555,10 +22555,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F36" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G36" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="37">
@@ -22573,7 +22573,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D37" t="n">
         <v>28.21085449100545</v>
@@ -22582,10 +22582,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F37" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G37" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="38">
@@ -22600,7 +22600,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D38" t="n">
         <v>28.21085449100545</v>
@@ -22609,10 +22609,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F38" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G38" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="39">
@@ -22627,7 +22627,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D39" t="n">
         <v>28.21085449100545</v>
@@ -22636,10 +22636,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F39" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G39" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="40">
@@ -22654,7 +22654,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D40" t="n">
         <v>28.21085449100545</v>
@@ -22663,10 +22663,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F40" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G40" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="41">
@@ -22681,7 +22681,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="D41" t="n">
         <v>28.21085449100545</v>
@@ -22690,10 +22690,10 @@
         <v>28.21085449100545</v>
       </c>
       <c r="F41" t="n">
-        <v>241.6931524547803</v>
+        <v>241.6931524547804</v>
       </c>
       <c r="G41" t="n">
-        <v>8.567381485443487</v>
+        <v>8.567381485443489</v>
       </c>
     </row>
     <row r="42">
@@ -23788,7 +23788,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D82" t="n">
         <v>28.74371242335771</v>
@@ -23797,10 +23797,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F82" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G82" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="83">
@@ -23815,7 +23815,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D83" t="n">
         <v>28.74371242335771</v>
@@ -23824,10 +23824,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F83" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G83" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="84">
@@ -23842,7 +23842,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D84" t="n">
         <v>28.74371242335771</v>
@@ -23851,10 +23851,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F84" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G84" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="85">
@@ -23869,7 +23869,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D85" t="n">
         <v>28.74371242335771</v>
@@ -23878,10 +23878,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F85" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G85" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="86">
@@ -23896,7 +23896,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D86" t="n">
         <v>28.74371242335771</v>
@@ -23905,10 +23905,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F86" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G86" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="87">
@@ -23923,7 +23923,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D87" t="n">
         <v>28.74371242335771</v>
@@ -23932,10 +23932,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F87" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G87" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="88">
@@ -23950,7 +23950,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D88" t="n">
         <v>28.74371242335771</v>
@@ -23959,10 +23959,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F88" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G88" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="89">
@@ -23977,7 +23977,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D89" t="n">
         <v>28.74371242335771</v>
@@ -23986,10 +23986,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F89" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G89" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="90">
@@ -24004,7 +24004,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D90" t="n">
         <v>28.74371242335771</v>
@@ -24013,10 +24013,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F90" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G90" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="91">
@@ -24031,7 +24031,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D91" t="n">
         <v>28.74371242335771</v>
@@ -24040,10 +24040,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F91" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G91" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="92">
@@ -24058,7 +24058,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D92" t="n">
         <v>28.74371242335771</v>
@@ -24067,10 +24067,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F92" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G92" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="93">
@@ -24085,7 +24085,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D93" t="n">
         <v>28.74371242335771</v>
@@ -24094,10 +24094,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F93" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G93" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="94">
@@ -24112,7 +24112,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D94" t="n">
         <v>28.74371242335771</v>
@@ -24121,10 +24121,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F94" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G94" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="95">
@@ -24139,7 +24139,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D95" t="n">
         <v>28.74371242335771</v>
@@ -24148,10 +24148,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F95" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G95" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="96">
@@ -24166,7 +24166,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D96" t="n">
         <v>28.74371242335771</v>
@@ -24175,10 +24175,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F96" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G96" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
     <row r="97">
@@ -24193,7 +24193,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="D97" t="n">
         <v>28.74371242335771</v>
@@ -24202,10 +24202,10 @@
         <v>28.74371242335771</v>
       </c>
       <c r="F97" t="n">
-        <v>212.8488372093023</v>
+        <v>212.8488372093024</v>
       </c>
       <c r="G97" t="n">
-        <v>7.405057289549598</v>
+        <v>7.405057289549599</v>
       </c>
     </row>
   </sheetData>
@@ -36682,16 +36682,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D70" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E70" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F70" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G70" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="71">
@@ -36709,16 +36709,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D71" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E71" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F71" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G71" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="72">
@@ -36736,16 +36736,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D72" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E72" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F72" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G72" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="73">
@@ -36763,16 +36763,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D73" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E73" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F73" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G73" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="74">
@@ -36790,16 +36790,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D74" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E74" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F74" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G74" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="75">
@@ -36817,16 +36817,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D75" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E75" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F75" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G75" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="76">
@@ -36844,16 +36844,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D76" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E76" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F76" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G76" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="77">
@@ -36871,16 +36871,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D77" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E77" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F77" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G77" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="78">
@@ -36898,16 +36898,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D78" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E78" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F78" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="79">
@@ -36925,16 +36925,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D79" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E79" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F79" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="80">
@@ -36952,16 +36952,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D80" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E80" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F80" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G80" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="81">
@@ -36979,16 +36979,16 @@
         <v>16.5954415954416</v>
       </c>
       <c r="D81" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="E81" t="n">
-        <v>20.56668924627179</v>
+        <v>20.5666892462718</v>
       </c>
       <c r="F81" t="n">
         <v>16.5954415954416</v>
       </c>
       <c r="G81" t="n">
-        <v>0.8069087540888439</v>
+        <v>0.8069087540888438</v>
       </c>
     </row>
     <row r="82">
@@ -37006,10 +37006,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D82" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E82" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F82" t="n">
         <v>200.2713675213675</v>
@@ -37033,10 +37033,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D83" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E83" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F83" t="n">
         <v>200.2713675213675</v>
@@ -37060,10 +37060,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D84" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E84" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F84" t="n">
         <v>200.2713675213675</v>
@@ -37087,10 +37087,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D85" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E85" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F85" t="n">
         <v>200.2713675213675</v>
@@ -37114,10 +37114,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D86" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E86" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F86" t="n">
         <v>200.2713675213675</v>
@@ -37141,10 +37141,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D87" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E87" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F87" t="n">
         <v>200.2713675213675</v>
@@ -37168,10 +37168,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D88" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E88" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F88" t="n">
         <v>200.2713675213675</v>
@@ -37195,10 +37195,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D89" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E89" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F89" t="n">
         <v>200.2713675213675</v>
@@ -37222,10 +37222,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D90" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E90" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F90" t="n">
         <v>200.2713675213675</v>
@@ -37249,10 +37249,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D91" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E91" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F91" t="n">
         <v>200.2713675213675</v>
@@ -37276,10 +37276,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D92" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E92" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F92" t="n">
         <v>200.2713675213675</v>
@@ -37303,10 +37303,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D93" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E93" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F93" t="n">
         <v>200.2713675213675</v>
@@ -37330,10 +37330,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D94" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E94" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F94" t="n">
         <v>200.2713675213675</v>
@@ -37357,10 +37357,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D95" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E95" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F95" t="n">
         <v>200.2713675213675</v>
@@ -37384,10 +37384,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D96" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E96" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F96" t="n">
         <v>200.2713675213675</v>
@@ -37411,10 +37411,10 @@
         <v>200.2713675213675</v>
       </c>
       <c r="D97" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="E97" t="n">
-        <v>19.45694415262075</v>
+        <v>19.45694415262076</v>
       </c>
       <c r="F97" t="n">
         <v>200.2713675213675</v>
@@ -37498,7 +37498,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="3">
@@ -37525,7 +37525,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G3" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="4">
@@ -37552,7 +37552,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G4" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="5">
@@ -37579,7 +37579,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="6">
@@ -38578,7 +38578,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G42" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="43">
@@ -38605,7 +38605,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G43" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="44">
@@ -38632,7 +38632,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G44" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="45">
@@ -38659,7 +38659,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G45" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="46">
@@ -38686,7 +38686,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G46" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="47">
@@ -38713,7 +38713,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G47" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="48">
@@ -38740,7 +38740,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G48" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="49">
@@ -38767,7 +38767,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G49" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="50">
@@ -38794,7 +38794,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G50" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="51">
@@ -38821,7 +38821,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G51" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="52">
@@ -38848,7 +38848,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G52" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="53">
@@ -38875,7 +38875,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G53" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="54">
@@ -38902,7 +38902,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G54" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="55">
@@ -38929,7 +38929,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G55" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="56">
@@ -38956,7 +38956,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G56" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="57">
@@ -38983,7 +38983,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G57" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="58">
@@ -39010,7 +39010,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G58" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="59">
@@ -39037,7 +39037,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G59" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="60">
@@ -39064,7 +39064,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G60" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="61">
@@ -39091,7 +39091,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G61" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="62">
@@ -39118,7 +39118,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G62" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="63">
@@ -39145,7 +39145,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G63" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="64">
@@ -39172,7 +39172,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G64" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="65">
@@ -39199,7 +39199,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G65" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="66">
@@ -39226,7 +39226,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G66" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="67">
@@ -39253,7 +39253,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G67" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="68">
@@ -39280,7 +39280,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G68" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="69">
@@ -39307,7 +39307,7 @@
         <v>43.79208333333333</v>
       </c>
       <c r="G69" t="n">
-        <v>2.250698460823391</v>
+        <v>2.250698460823392</v>
       </c>
     </row>
     <row r="70">
@@ -39649,10 +39649,10 @@
         <v>209.725</v>
       </c>
       <c r="D82" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E82" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F82" t="n">
         <v>209.725</v>
@@ -39676,10 +39676,10 @@
         <v>209.725</v>
       </c>
       <c r="D83" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E83" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F83" t="n">
         <v>209.725</v>
@@ -39703,10 +39703,10 @@
         <v>209.725</v>
       </c>
       <c r="D84" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E84" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F84" t="n">
         <v>209.725</v>
@@ -39730,10 +39730,10 @@
         <v>209.725</v>
       </c>
       <c r="D85" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E85" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F85" t="n">
         <v>209.725</v>
@@ -39757,10 +39757,10 @@
         <v>209.725</v>
       </c>
       <c r="D86" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E86" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F86" t="n">
         <v>209.725</v>
@@ -39784,10 +39784,10 @@
         <v>209.725</v>
       </c>
       <c r="D87" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E87" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F87" t="n">
         <v>209.725</v>
@@ -39811,10 +39811,10 @@
         <v>209.725</v>
       </c>
       <c r="D88" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E88" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F88" t="n">
         <v>209.725</v>
@@ -39838,10 +39838,10 @@
         <v>209.725</v>
       </c>
       <c r="D89" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E89" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F89" t="n">
         <v>209.725</v>
@@ -39865,10 +39865,10 @@
         <v>209.725</v>
       </c>
       <c r="D90" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E90" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F90" t="n">
         <v>209.725</v>
@@ -39892,10 +39892,10 @@
         <v>209.725</v>
       </c>
       <c r="D91" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E91" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F91" t="n">
         <v>209.725</v>
@@ -39919,10 +39919,10 @@
         <v>209.725</v>
       </c>
       <c r="D92" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E92" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F92" t="n">
         <v>209.725</v>
@@ -39946,10 +39946,10 @@
         <v>209.725</v>
       </c>
       <c r="D93" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E93" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F93" t="n">
         <v>209.725</v>
@@ -39973,10 +39973,10 @@
         <v>209.725</v>
       </c>
       <c r="D94" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E94" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F94" t="n">
         <v>209.725</v>
@@ -40000,10 +40000,10 @@
         <v>209.725</v>
       </c>
       <c r="D95" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E95" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F95" t="n">
         <v>209.725</v>
@@ -40027,10 +40027,10 @@
         <v>209.725</v>
       </c>
       <c r="D96" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E96" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F96" t="n">
         <v>209.725</v>
@@ -40054,10 +40054,10 @@
         <v>209.725</v>
       </c>
       <c r="D97" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="E97" t="n">
-        <v>18.53050491684343</v>
+        <v>18.53050491684344</v>
       </c>
       <c r="F97" t="n">
         <v>209.725</v>
@@ -42775,10 +42775,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D2" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E2" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F2" t="n">
         <v>107.2952044025157</v>
@@ -42802,10 +42802,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D3" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E3" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F3" t="n">
         <v>107.2952044025157</v>
@@ -42829,10 +42829,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D4" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E4" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F4" t="n">
         <v>107.2952044025157</v>
@@ -42856,10 +42856,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D5" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E5" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F5" t="n">
         <v>107.2952044025157</v>
@@ -43423,10 +43423,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D26" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E26" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F26" t="n">
         <v>356.122248427673</v>
@@ -43450,10 +43450,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D27" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E27" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F27" t="n">
         <v>356.122248427673</v>
@@ -43477,10 +43477,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D28" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E28" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F28" t="n">
         <v>356.122248427673</v>
@@ -43504,10 +43504,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D29" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E29" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F29" t="n">
         <v>356.122248427673</v>
@@ -43531,10 +43531,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D30" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E30" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F30" t="n">
         <v>356.122248427673</v>
@@ -43558,10 +43558,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D31" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E31" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F31" t="n">
         <v>356.122248427673</v>
@@ -43585,10 +43585,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D32" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E32" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F32" t="n">
         <v>356.122248427673</v>
@@ -43612,10 +43612,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D33" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E33" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F33" t="n">
         <v>356.122248427673</v>
@@ -43639,10 +43639,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D34" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E34" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F34" t="n">
         <v>356.122248427673</v>
@@ -43666,10 +43666,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D35" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E35" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F35" t="n">
         <v>356.122248427673</v>
@@ -43693,10 +43693,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D36" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E36" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F36" t="n">
         <v>356.122248427673</v>
@@ -43720,10 +43720,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D37" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E37" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F37" t="n">
         <v>356.122248427673</v>
@@ -43747,10 +43747,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D38" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E38" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F38" t="n">
         <v>356.122248427673</v>
@@ -43774,10 +43774,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D39" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E39" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F39" t="n">
         <v>356.122248427673</v>
@@ -43801,10 +43801,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D40" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E40" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F40" t="n">
         <v>356.122248427673</v>
@@ -43828,10 +43828,10 @@
         <v>356.122248427673</v>
       </c>
       <c r="D41" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="E41" t="n">
-        <v>22.82445860647418</v>
+        <v>22.82445860647417</v>
       </c>
       <c r="F41" t="n">
         <v>356.122248427673</v>
@@ -43855,10 +43855,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D42" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E42" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F42" t="n">
         <v>107.2952044025157</v>
@@ -43882,10 +43882,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D43" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E43" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F43" t="n">
         <v>107.2952044025157</v>
@@ -43909,10 +43909,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D44" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E44" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F44" t="n">
         <v>107.2952044025157</v>
@@ -43936,10 +43936,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D45" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E45" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F45" t="n">
         <v>107.2952044025157</v>
@@ -43963,10 +43963,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D46" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E46" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F46" t="n">
         <v>107.2952044025157</v>
@@ -43990,10 +43990,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D47" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E47" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F47" t="n">
         <v>107.2952044025157</v>
@@ -44017,10 +44017,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D48" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E48" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F48" t="n">
         <v>107.2952044025157</v>
@@ -44044,10 +44044,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D49" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E49" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F49" t="n">
         <v>107.2952044025157</v>
@@ -44071,10 +44071,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D50" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E50" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F50" t="n">
         <v>107.2952044025157</v>
@@ -44098,10 +44098,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D51" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E51" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F51" t="n">
         <v>107.2952044025157</v>
@@ -44125,10 +44125,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D52" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E52" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F52" t="n">
         <v>107.2952044025157</v>
@@ -44152,10 +44152,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D53" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E53" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F53" t="n">
         <v>107.2952044025157</v>
@@ -44179,10 +44179,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D54" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E54" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F54" t="n">
         <v>107.2952044025157</v>
@@ -44206,10 +44206,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D55" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E55" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F55" t="n">
         <v>107.2952044025157</v>
@@ -44233,10 +44233,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D56" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E56" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F56" t="n">
         <v>107.2952044025157</v>
@@ -44260,10 +44260,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D57" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E57" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F57" t="n">
         <v>107.2952044025157</v>
@@ -44287,10 +44287,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D58" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E58" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F58" t="n">
         <v>107.2952044025157</v>
@@ -44314,10 +44314,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D59" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E59" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F59" t="n">
         <v>107.2952044025157</v>
@@ -44341,10 +44341,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D60" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E60" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F60" t="n">
         <v>107.2952044025157</v>
@@ -44368,10 +44368,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D61" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E61" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F61" t="n">
         <v>107.2952044025157</v>
@@ -44395,10 +44395,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D62" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E62" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F62" t="n">
         <v>107.2952044025157</v>
@@ -44422,10 +44422,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D63" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E63" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F63" t="n">
         <v>107.2952044025157</v>
@@ -44449,10 +44449,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D64" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E64" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F64" t="n">
         <v>107.2952044025157</v>
@@ -44476,10 +44476,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D65" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E65" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F65" t="n">
         <v>107.2952044025157</v>
@@ -44503,10 +44503,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D66" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E66" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F66" t="n">
         <v>107.2952044025157</v>
@@ -44530,10 +44530,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D67" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E67" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F67" t="n">
         <v>107.2952044025157</v>
@@ -44557,10 +44557,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D68" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E68" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F68" t="n">
         <v>107.2952044025157</v>
@@ -44584,10 +44584,10 @@
         <v>107.2952044025157</v>
       </c>
       <c r="D69" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="E69" t="n">
-        <v>26.57599923091091</v>
+        <v>26.57599923091092</v>
       </c>
       <c r="F69" t="n">
         <v>107.2952044025157</v>
@@ -45427,7 +45427,7 @@
         <v>36.05625</v>
       </c>
       <c r="G2" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="3">
@@ -45454,7 +45454,7 @@
         <v>36.05625</v>
       </c>
       <c r="G3" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="4">
@@ -45481,7 +45481,7 @@
         <v>36.05625</v>
       </c>
       <c r="G4" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="5">
@@ -45508,7 +45508,7 @@
         <v>36.05625</v>
       </c>
       <c r="G5" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="6">
@@ -45535,7 +45535,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G6" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="7">
@@ -45562,7 +45562,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G7" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="8">
@@ -45589,7 +45589,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G8" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="9">
@@ -45616,7 +45616,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G9" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="10">
@@ -45643,7 +45643,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G10" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="11">
@@ -45670,7 +45670,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G11" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="12">
@@ -45697,7 +45697,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G12" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="13">
@@ -45724,7 +45724,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G13" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="14">
@@ -45751,7 +45751,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G14" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="15">
@@ -45778,7 +45778,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G15" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="16">
@@ -45805,7 +45805,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G16" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="17">
@@ -45832,7 +45832,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G17" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="18">
@@ -45859,7 +45859,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G18" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="19">
@@ -45886,7 +45886,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G19" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="20">
@@ -45913,7 +45913,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G20" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="21">
@@ -45940,7 +45940,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G21" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="22">
@@ -45967,7 +45967,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G22" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="23">
@@ -45994,7 +45994,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G23" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="24">
@@ -46021,7 +46021,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G24" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="25">
@@ -46048,7 +46048,7 @@
         <v>158.0051724137931</v>
       </c>
       <c r="G25" t="n">
-        <v>8.63938805800163</v>
+        <v>8.639388058001629</v>
       </c>
     </row>
     <row r="26">
@@ -46507,7 +46507,7 @@
         <v>36.05625</v>
       </c>
       <c r="G42" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="43">
@@ -46534,7 +46534,7 @@
         <v>36.05625</v>
       </c>
       <c r="G43" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="44">
@@ -46561,7 +46561,7 @@
         <v>36.05625</v>
       </c>
       <c r="G44" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="45">
@@ -46588,7 +46588,7 @@
         <v>36.05625</v>
       </c>
       <c r="G45" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="46">
@@ -46615,7 +46615,7 @@
         <v>36.05625</v>
       </c>
       <c r="G46" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="47">
@@ -46642,7 +46642,7 @@
         <v>36.05625</v>
       </c>
       <c r="G47" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="48">
@@ -46669,7 +46669,7 @@
         <v>36.05625</v>
       </c>
       <c r="G48" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="49">
@@ -46696,7 +46696,7 @@
         <v>36.05625</v>
       </c>
       <c r="G49" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="50">
@@ -46723,7 +46723,7 @@
         <v>36.05625</v>
       </c>
       <c r="G50" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="51">
@@ -46750,7 +46750,7 @@
         <v>36.05625</v>
       </c>
       <c r="G51" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="52">
@@ -46777,7 +46777,7 @@
         <v>36.05625</v>
       </c>
       <c r="G52" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="53">
@@ -46804,7 +46804,7 @@
         <v>36.05625</v>
       </c>
       <c r="G53" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="54">
@@ -46831,7 +46831,7 @@
         <v>36.05625</v>
       </c>
       <c r="G54" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="55">
@@ -46858,7 +46858,7 @@
         <v>36.05625</v>
       </c>
       <c r="G55" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="56">
@@ -46885,7 +46885,7 @@
         <v>36.05625</v>
       </c>
       <c r="G56" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="57">
@@ -46912,7 +46912,7 @@
         <v>36.05625</v>
       </c>
       <c r="G57" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="58">
@@ -46939,7 +46939,7 @@
         <v>36.05625</v>
       </c>
       <c r="G58" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="59">
@@ -46966,7 +46966,7 @@
         <v>36.05625</v>
       </c>
       <c r="G59" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="60">
@@ -46993,7 +46993,7 @@
         <v>36.05625</v>
       </c>
       <c r="G60" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="61">
@@ -47020,7 +47020,7 @@
         <v>36.05625</v>
       </c>
       <c r="G61" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="62">
@@ -47047,7 +47047,7 @@
         <v>36.05625</v>
       </c>
       <c r="G62" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="63">
@@ -47074,7 +47074,7 @@
         <v>36.05625</v>
       </c>
       <c r="G63" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="64">
@@ -47101,7 +47101,7 @@
         <v>36.05625</v>
       </c>
       <c r="G64" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="65">
@@ -47128,7 +47128,7 @@
         <v>36.05625</v>
       </c>
       <c r="G65" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="66">
@@ -47155,7 +47155,7 @@
         <v>36.05625</v>
       </c>
       <c r="G66" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="67">
@@ -47182,7 +47182,7 @@
         <v>36.05625</v>
       </c>
       <c r="G67" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="68">
@@ -47209,7 +47209,7 @@
         <v>36.05625</v>
       </c>
       <c r="G68" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="69">
@@ -47236,7 +47236,7 @@
         <v>36.05625</v>
       </c>
       <c r="G69" t="n">
-        <v>1.900268150755487</v>
+        <v>1.900268150755486</v>
       </c>
     </row>
     <row r="70">
@@ -50704,16 +50704,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D2" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E2" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F2" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G2" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="3">
@@ -50731,16 +50731,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D3" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E3" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F3" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G3" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="4">
@@ -50758,16 +50758,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D4" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E4" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F4" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G4" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="5">
@@ -50785,16 +50785,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D5" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E5" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F5" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G5" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="6">
@@ -50812,16 +50812,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D6" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E6" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F6" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G6" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="7">
@@ -50839,16 +50839,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D7" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E7" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F7" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G7" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="8">
@@ -50866,16 +50866,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D8" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E8" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F8" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G8" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="9">
@@ -50893,16 +50893,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D9" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E9" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F9" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G9" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="10">
@@ -50920,16 +50920,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D10" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E10" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F10" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G10" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="11">
@@ -50947,16 +50947,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D11" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E11" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F11" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G11" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="12">
@@ -50974,16 +50974,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D12" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E12" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F12" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G12" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="13">
@@ -51001,16 +51001,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D13" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E13" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F13" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G13" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="14">
@@ -51028,16 +51028,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D14" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E14" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F14" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G14" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="15">
@@ -51055,16 +51055,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D15" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E15" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F15" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G15" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="16">
@@ -51082,16 +51082,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D16" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E16" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F16" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G16" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="17">
@@ -51109,16 +51109,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D17" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E17" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F17" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G17" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="18">
@@ -51136,16 +51136,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D18" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E18" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F18" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G18" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="19">
@@ -51163,16 +51163,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D19" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E19" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F19" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G19" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="20">
@@ -51190,16 +51190,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D20" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E20" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F20" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G20" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="21">
@@ -51217,16 +51217,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D21" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E21" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F21" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G21" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="22">
@@ -51244,16 +51244,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D22" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E22" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F22" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G22" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="23">
@@ -51271,16 +51271,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D23" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E23" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F23" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G23" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="24">
@@ -51298,16 +51298,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D24" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E24" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F24" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G24" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="25">
@@ -51325,16 +51325,16 @@
         <v>410.8431154381085</v>
       </c>
       <c r="D25" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="E25" t="n">
-        <v>28.53919974628626</v>
+        <v>28.53919974628625</v>
       </c>
       <c r="F25" t="n">
         <v>410.8431154381085</v>
       </c>
       <c r="G25" t="n">
-        <v>14.39574757142833</v>
+        <v>14.39574757142834</v>
       </c>
     </row>
     <row r="26">
@@ -51784,16 +51784,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D42" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E42" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F42" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G42" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="43">
@@ -51811,16 +51811,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D43" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E43" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F43" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G43" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="44">
@@ -51838,16 +51838,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D44" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E44" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F44" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G44" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="45">
@@ -51865,16 +51865,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D45" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E45" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F45" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G45" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="46">
@@ -51892,16 +51892,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D46" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E46" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F46" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G46" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="47">
@@ -51919,16 +51919,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D47" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E47" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F47" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G47" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="48">
@@ -51946,16 +51946,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D48" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E48" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F48" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G48" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="49">
@@ -51973,16 +51973,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D49" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E49" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F49" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G49" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="50">
@@ -52000,16 +52000,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D50" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E50" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F50" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G50" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="51">
@@ -52027,16 +52027,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D51" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E51" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F51" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G51" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="52">
@@ -52054,16 +52054,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D52" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E52" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F52" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G52" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="53">
@@ -52081,16 +52081,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D53" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E53" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F53" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G53" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="54">
@@ -52108,16 +52108,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D54" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E54" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F54" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G54" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="55">
@@ -52135,16 +52135,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D55" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E55" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F55" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G55" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="56">
@@ -52162,16 +52162,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D56" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E56" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F56" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G56" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="57">
@@ -52189,16 +52189,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D57" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E57" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F57" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G57" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="58">
@@ -52216,16 +52216,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D58" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E58" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F58" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G58" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="59">
@@ -52243,16 +52243,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D59" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E59" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F59" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G59" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="60">
@@ -52270,16 +52270,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D60" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E60" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F60" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G60" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="61">
@@ -52297,16 +52297,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D61" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E61" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F61" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G61" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="62">
@@ -52324,16 +52324,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D62" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E62" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F62" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G62" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="63">
@@ -52351,16 +52351,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D63" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E63" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F63" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G63" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="64">
@@ -52378,16 +52378,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D64" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E64" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F64" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G64" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="65">
@@ -52405,16 +52405,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D65" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E65" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F65" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G65" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="66">
@@ -52432,16 +52432,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D66" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E66" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F66" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G66" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="67">
@@ -52459,16 +52459,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D67" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E67" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F67" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G67" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="68">
@@ -52486,16 +52486,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D68" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E68" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F68" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G68" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="69">
@@ -52513,16 +52513,16 @@
         <v>158.8311891515994</v>
       </c>
       <c r="D69" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="E69" t="n">
-        <v>30.38925390440567</v>
+        <v>30.38925390440568</v>
       </c>
       <c r="F69" t="n">
         <v>158.8311891515994</v>
       </c>
       <c r="G69" t="n">
-        <v>5.226557705274</v>
+        <v>5.226557705273998</v>
       </c>
     </row>
     <row r="70">
